--- a/data/Hexane+PDMS-new.xlsx
+++ b/data/Hexane+PDMS-new.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexg\Downloads\Pitt-ML-MSE-Project\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED7B5F5-13FA-4DAB-93EB-561CBC6FBCEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="855" yWindow="1065" windowWidth="19440" windowHeight="15600" activeTab="5"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="11-(7,13)-2025" sheetId="1" r:id="rId1"/>
@@ -21,7 +27,7 @@
     <externalReference r:id="rId10"/>
     <externalReference r:id="rId11"/>
   </externalReferences>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -1048,7 +1054,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
@@ -1177,7 +1183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -1197,28 +1203,10 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1230,11 +1218,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1254,7 +1254,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1280,7 +1280,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1392,7 +1391,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-A986-B84F-A567-40BA1DFC23B6}"/>
             </c:ext>
@@ -1491,7 +1490,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-A986-B84F-A567-40BA1DFC23B6}"/>
             </c:ext>
@@ -1590,7 +1589,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-A986-B84F-A567-40BA1DFC23B6}"/>
             </c:ext>
@@ -1776,7 +1775,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1913,7 +1912,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-0659-6747-84F6-18980F779C3A}"/>
             </c:ext>
@@ -2012,7 +2011,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-0659-6747-84F6-18980F779C3A}"/>
             </c:ext>
@@ -2111,7 +2110,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-0659-6747-84F6-18980F779C3A}"/>
             </c:ext>
@@ -2297,7 +2296,7 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2341,6 +2340,26 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -2435,7 +2454,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-9A7B-F64D-8B90-63CB7BD3047B}"/>
             </c:ext>
@@ -2528,7 +2547,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-9A7B-F64D-8B90-63CB7BD3047B}"/>
             </c:ext>
@@ -2600,6 +2619,23 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="in"/>
@@ -2685,6 +2721,23 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="in"/>
@@ -2804,7 +2857,7 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2848,6 +2901,26 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -2982,7 +3055,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-28D9-5E48-9E04-EEAA54F85C81}"/>
             </c:ext>
@@ -3105,7 +3178,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-28D9-5E48-9E04-EEAA54F85C81}"/>
             </c:ext>
@@ -3234,7 +3307,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-28D9-5E48-9E04-EEAA54F85C81}"/>
             </c:ext>
@@ -3303,6 +3376,26 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="in"/>
@@ -3395,6 +3488,23 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="in"/>
@@ -3514,7 +3624,7 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -3558,6 +3668,26 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -3694,7 +3824,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-26A2-F641-9C0C-8B9195AD460C}"/>
             </c:ext>
@@ -3829,7 +3959,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-26A2-F641-9C0C-8B9195AD460C}"/>
             </c:ext>
@@ -3964,7 +4094,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-26A2-F641-9C0C-8B9195AD460C}"/>
             </c:ext>
@@ -4028,6 +4158,23 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="in"/>
@@ -4112,6 +4259,23 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="in"/>
@@ -4231,7 +4395,7 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -4396,7 +4560,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-8503-1045-A3A2-5BA208C1DAA3}"/>
             </c:ext>
@@ -4538,7 +4702,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-8503-1045-A3A2-5BA208C1DAA3}"/>
             </c:ext>
@@ -4680,7 +4844,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-8503-1045-A3A2-5BA208C1DAA3}"/>
             </c:ext>
@@ -6474,7 +6638,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40D994C5-2EF2-7A40-A3C5-7B21DD96887F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40D994C5-2EF2-7A40-A3C5-7B21DD96887F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6512,7 +6676,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A14FB8FD-45D9-6048-9047-A31284121567}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A14FB8FD-45D9-6048-9047-A31284121567}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6545,7 +6709,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AA21783-02C8-674E-BC7D-A90F5F86C4E2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AA21783-02C8-674E-BC7D-A90F5F86C4E2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6578,7 +6742,7 @@
         <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFF8B5A8-FD33-074D-9CB5-84C50CE4C0B2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFF8B5A8-FD33-074D-9CB5-84C50CE4C0B2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6611,7 +6775,7 @@
         <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2F44452-B447-E34C-A68A-4D5B19B08F24}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2F44452-B447-E34C-A68A-4D5B19B08F24}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6649,7 +6813,7 @@
         <xdr:cNvPr id="6" name="Chart 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2DCCD51-8D10-CA4C-A38B-02EA65B419BD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2DCCD51-8D10-CA4C-A38B-02EA65B419BD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6673,7 +6837,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="PDMS Data"/>
@@ -6810,7 +6974,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Hexane Data"/>
@@ -6887,7 +7051,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Hexane Data"/>
@@ -7052,7 +7216,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Hexane Data"/>
@@ -7245,7 +7409,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Data"/>
@@ -7469,9 +7633,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7509,7 +7673,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -7581,7 +7745,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7754,20 +7918,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE55"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" t="s">
@@ -7793,38 +7957,38 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
-      <c r="U3" s="19" t="s">
+      <c r="U3" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="20"/>
-      <c r="Y3" s="20"/>
-      <c r="Z3" s="20"/>
-      <c r="AA3" s="20"/>
-      <c r="AB3" s="20"/>
-      <c r="AC3" s="20"/>
-      <c r="AD3" s="20"/>
-      <c r="AE3" s="20"/>
-    </row>
-    <row r="4" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="V3" s="22"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
+      <c r="Y3" s="22"/>
+      <c r="Z3" s="22"/>
+      <c r="AA3" s="22"/>
+      <c r="AB3" s="22"/>
+      <c r="AC3" s="22"/>
+      <c r="AD3" s="22"/>
+      <c r="AE3" s="22"/>
+    </row>
+    <row r="4" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
       <c r="Z4" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -7850,7 +8014,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -7876,7 +8040,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -7902,7 +8066,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -7928,7 +8092,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -7954,7 +8118,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -7980,7 +8144,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -8038,24 +8202,24 @@
         <v>1.4366666666666665</v>
       </c>
     </row>
-    <row r="13" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+    <row r="13" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
       <c r="T13" s="4" t="s">
         <v>101</v>
       </c>
@@ -8063,41 +8227,41 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
         <v>0.1</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="E14" s="15">
+      <c r="B14" s="19"/>
+      <c r="E14" s="19">
         <v>0.15</v>
       </c>
-      <c r="F14" s="15"/>
-      <c r="I14" s="15">
+      <c r="F14" s="19"/>
+      <c r="I14" s="19">
         <v>0.25</v>
       </c>
-      <c r="J14" s="15"/>
-      <c r="M14" s="15">
+      <c r="J14" s="19"/>
+      <c r="M14" s="19">
         <v>0.5</v>
       </c>
-      <c r="N14" s="15"/>
-      <c r="Q14" s="15">
+      <c r="N14" s="19"/>
+      <c r="Q14" s="19">
         <v>1</v>
       </c>
-      <c r="R14" s="15"/>
-      <c r="U14" s="15">
+      <c r="R14" s="19"/>
+      <c r="U14" s="19">
         <v>2.5</v>
       </c>
-      <c r="V14" s="15"/>
-      <c r="Y14" s="15">
+      <c r="V14" s="19"/>
+      <c r="Y14" s="19">
         <v>3</v>
       </c>
-      <c r="Z14" s="15"/>
-      <c r="AC14" s="15">
+      <c r="Z14" s="19"/>
+      <c r="AC14" s="19">
         <v>5</v>
       </c>
-      <c r="AD14" s="15"/>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AD14" s="19"/>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -8123,7 +8287,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -8149,7 +8313,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -8175,7 +8339,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -8201,7 +8365,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -8227,7 +8391,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -8253,7 +8417,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
@@ -8311,7 +8475,7 @@
         <v>6.4833333333333334</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -8369,58 +8533,58 @@
         <v>1.527525231651947E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+    <row r="23" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
       <c r="T23" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A24" s="19">
         <v>0.1</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="E24" s="15">
+      <c r="B24" s="19"/>
+      <c r="E24" s="19">
         <v>0.15</v>
       </c>
-      <c r="F24" s="15"/>
-      <c r="I24" s="15">
+      <c r="F24" s="19"/>
+      <c r="I24" s="19">
         <v>0.25</v>
       </c>
-      <c r="J24" s="15"/>
-      <c r="M24" s="15">
+      <c r="J24" s="19"/>
+      <c r="M24" s="19">
         <v>0.5</v>
       </c>
-      <c r="N24" s="15"/>
-      <c r="Q24" s="15">
+      <c r="N24" s="19"/>
+      <c r="Q24" s="19">
         <v>1</v>
       </c>
-      <c r="R24" s="15"/>
-      <c r="U24" s="15">
+      <c r="R24" s="19"/>
+      <c r="U24" s="19">
         <v>2.5</v>
       </c>
-      <c r="V24" s="15"/>
-      <c r="Y24" s="15">
+      <c r="V24" s="19"/>
+      <c r="Y24" s="19">
         <v>3</v>
       </c>
-      <c r="Z24" s="15"/>
-      <c r="AC24" s="15">
+      <c r="Z24" s="19"/>
+      <c r="AC24" s="19">
         <v>5</v>
       </c>
-      <c r="AD24" s="15"/>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AD24" s="19"/>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>51</v>
       </c>
@@ -8446,7 +8610,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>52</v>
       </c>
@@ -8472,7 +8636,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -8498,7 +8662,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>54</v>
       </c>
@@ -8524,7 +8688,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>55</v>
       </c>
@@ -8550,7 +8714,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -8576,7 +8740,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
@@ -8634,7 +8798,7 @@
         <v>0.55333333333333334</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>28</v>
       </c>
@@ -8692,12 +8856,12 @@
         <v>1.5275252316519464E-3</v>
       </c>
     </row>
-    <row r="33" spans="2:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:30" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="T33" s="4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B34" s="10">
         <f>B21-B31</f>
         <v>0.42</v>
@@ -8731,169 +8895,169 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C35" s="17" t="s">
+    <row r="35" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C35" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17" t="s">
+      <c r="D35" s="18"/>
+      <c r="E35" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17" t="s">
+      <c r="F35" s="18"/>
+      <c r="G35" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
       <c r="J35" s="9" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="36" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C36" s="18">
+    <row r="36" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C36" s="14">
         <v>0.1</v>
       </c>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18" t="s">
+      <c r="D36" s="14"/>
+      <c r="E36" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18" t="s">
+      <c r="F36" s="14"/>
+      <c r="G36" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
       <c r="J36" s="8">
         <v>0.42</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C37" s="18">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C37" s="14">
         <v>0.15</v>
       </c>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18" t="s">
+      <c r="D37" s="14"/>
+      <c r="E37" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18" t="s">
+      <c r="F37" s="14"/>
+      <c r="G37" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
       <c r="J37" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C38" s="18">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C38" s="14">
         <v>0.25</v>
       </c>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18" t="s">
+      <c r="D38" s="14"/>
+      <c r="E38" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18" t="s">
+      <c r="F38" s="14"/>
+      <c r="G38" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
       <c r="J38" s="8">
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C39" s="18">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C39" s="14">
         <v>0.5</v>
       </c>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18" t="s">
+      <c r="D39" s="14"/>
+      <c r="E39" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18" t="s">
+      <c r="F39" s="14"/>
+      <c r="G39" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
       <c r="J39" s="8">
         <v>0.78</v>
       </c>
     </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C40" s="18">
+    <row r="40" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C40" s="14">
         <v>1</v>
       </c>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18" t="s">
+      <c r="D40" s="14"/>
+      <c r="E40" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18" t="s">
+      <c r="F40" s="14"/>
+      <c r="G40" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
       <c r="J40" s="8">
         <v>1.43</v>
       </c>
     </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C41" s="18">
+    <row r="41" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C41" s="14">
         <v>2.5</v>
       </c>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18" t="s">
+      <c r="D41" s="14"/>
+      <c r="E41" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="F41" s="18"/>
-      <c r="G41" s="21" t="s">
+      <c r="F41" s="14"/>
+      <c r="G41" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="H41" s="22"/>
-      <c r="I41" s="23"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="17"/>
       <c r="J41" s="8">
         <v>3.02</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C42" s="18">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C42" s="14">
         <v>3</v>
       </c>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18" t="s">
+      <c r="D42" s="14"/>
+      <c r="E42" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18" t="s">
+      <c r="F42" s="14"/>
+      <c r="G42" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
       <c r="J42" s="8">
         <v>3.67</v>
       </c>
     </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C43" s="18">
+    <row r="43" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C43" s="14">
         <v>5</v>
       </c>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18" t="s">
+      <c r="D43" s="14"/>
+      <c r="E43" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18" t="s">
+      <c r="F43" s="14"/>
+      <c r="G43" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
       <c r="J43" s="8">
         <v>5.93</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.3">
       <c r="C47" s="11" t="s">
         <v>163</v>
       </c>
@@ -8907,7 +9071,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:30" x14ac:dyDescent="0.3">
       <c r="C48">
         <v>0.1</v>
       </c>
@@ -8921,7 +9085,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C49">
         <v>0.15</v>
       </c>
@@ -8935,7 +9099,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C50">
         <v>0.25</v>
       </c>
@@ -8949,7 +9113,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="51" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C51">
         <v>0.5</v>
       </c>
@@ -8963,7 +9127,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="52" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C52">
         <v>1</v>
       </c>
@@ -8977,7 +9141,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="53" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C53">
         <v>2.5</v>
       </c>
@@ -8991,7 +9155,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="54" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C54">
         <v>3</v>
       </c>
@@ -9005,7 +9169,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="55" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C55">
         <v>5</v>
       </c>
@@ -9021,6 +9185,37 @@
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="G40:I40"/>
     <mergeCell ref="U3:AE3"/>
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="C42:D42"/>
@@ -9037,37 +9232,6 @@
     <mergeCell ref="Y24:Z24"/>
     <mergeCell ref="AC14:AD14"/>
     <mergeCell ref="AC24:AD24"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9076,15 +9240,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F122"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>163</v>
       </c>
@@ -9098,7 +9262,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0.1</v>
       </c>
@@ -9112,7 +9276,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.15</v>
       </c>
@@ -9126,7 +9290,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.25</v>
       </c>
@@ -9140,7 +9304,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.5</v>
       </c>
@@ -9154,7 +9318,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -9168,7 +9332,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2.5</v>
       </c>
@@ -9182,7 +9346,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3</v>
       </c>
@@ -9196,7 +9360,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>5</v>
       </c>
@@ -9210,7 +9374,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>163</v>
       </c>
@@ -9227,7 +9391,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>0.1</v>
       </c>
@@ -9244,7 +9408,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>0.15</v>
       </c>
@@ -9261,7 +9425,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>0.25</v>
       </c>
@@ -9278,7 +9442,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>0.5</v>
       </c>
@@ -9295,7 +9459,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1</v>
       </c>
@@ -9312,7 +9476,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>163</v>
       </c>
@@ -9332,7 +9496,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>0.1</v>
       </c>
@@ -9352,7 +9516,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>0.15</v>
       </c>
@@ -9372,7 +9536,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>0.25</v>
       </c>
@@ -9392,7 +9556,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>0.5</v>
       </c>
@@ -9412,7 +9576,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1</v>
       </c>
@@ -9432,7 +9596,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1.5</v>
       </c>
@@ -9452,7 +9616,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>2</v>
       </c>
@@ -9472,7 +9636,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>2.5</v>
       </c>
@@ -9492,7 +9656,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>3</v>
       </c>
@@ -9512,7 +9676,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>5</v>
       </c>
@@ -9532,7 +9696,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="11" t="s">
         <v>163</v>
       </c>
@@ -9552,7 +9716,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>0.1</v>
       </c>
@@ -9572,7 +9736,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>0.15</v>
       </c>
@@ -9592,7 +9756,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>0.25</v>
       </c>
@@ -9612,7 +9776,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>0.5</v>
       </c>
@@ -9632,7 +9796,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1</v>
       </c>
@@ -9652,7 +9816,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1.5</v>
       </c>
@@ -9672,7 +9836,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>2</v>
       </c>
@@ -9692,7 +9856,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>2.5</v>
       </c>
@@ -9712,7 +9876,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>3</v>
       </c>
@@ -9732,7 +9896,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>5</v>
       </c>
@@ -9752,7 +9916,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>7</v>
       </c>
@@ -9772,7 +9936,7 @@
         <v>9.2899999999999991</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>10</v>
       </c>
@@ -9792,7 +9956,7 @@
         <v>12.67</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="11" t="s">
         <v>163</v>
       </c>
@@ -9806,7 +9970,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>0.02</v>
       </c>
@@ -9820,7 +9984,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>0.05</v>
       </c>
@@ -9834,7 +9998,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>7.0000000000000007E-2</v>
       </c>
@@ -9848,7 +10012,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>0.1</v>
       </c>
@@ -9862,7 +10026,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>0.15</v>
       </c>
@@ -9876,7 +10040,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>0.25</v>
       </c>
@@ -9890,7 +10054,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>0.5</v>
       </c>
@@ -9904,7 +10068,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>1</v>
       </c>
@@ -9918,7 +10082,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>1.5</v>
       </c>
@@ -9932,7 +10096,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>2</v>
       </c>
@@ -9946,7 +10110,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>2.5</v>
       </c>
@@ -9960,7 +10124,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>3</v>
       </c>
@@ -9974,7 +10138,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>5</v>
       </c>
@@ -9988,7 +10152,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>7</v>
       </c>
@@ -10002,7 +10166,7 @@
         <v>9.2899999999999991</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>10</v>
       </c>
@@ -10023,36 +10187,36 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P40"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>45978</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
@@ -10060,7 +10224,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>165</v>
       </c>
@@ -10074,7 +10238,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>166</v>
       </c>
@@ -10088,7 +10252,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>167</v>
       </c>
@@ -10102,7 +10266,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>168</v>
       </c>
@@ -10116,7 +10280,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>169</v>
       </c>
@@ -10130,7 +10294,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>170</v>
       </c>
@@ -10144,7 +10308,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -10174,45 +10338,45 @@
         <v>1.4766666666666666</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
       <c r="P13" s="4"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
         <v>1.5</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="E14" s="15">
+      <c r="B14" s="19"/>
+      <c r="E14" s="19">
         <v>2</v>
       </c>
-      <c r="F14" s="15"/>
-      <c r="I14" s="15">
+      <c r="F14" s="19"/>
+      <c r="I14" s="19">
         <v>7</v>
       </c>
-      <c r="J14" s="15"/>
-      <c r="M14" s="15">
+      <c r="J14" s="19"/>
+      <c r="M14" s="19">
         <v>10</v>
       </c>
-      <c r="N14" s="15"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N14" s="19"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>186</v>
       </c>
@@ -10226,7 +10390,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>187</v>
       </c>
@@ -10240,7 +10404,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>188</v>
       </c>
@@ -10254,7 +10418,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>189</v>
       </c>
@@ -10268,7 +10432,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -10282,7 +10446,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>190</v>
       </c>
@@ -10296,7 +10460,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
@@ -10326,7 +10490,7 @@
         <v>13.176666666666668</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -10355,19 +10519,19 @@
         <v>5.7735026918962525E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -10375,25 +10539,25 @@
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="19">
         <v>1.5</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="E24" s="15">
+      <c r="B24" s="19"/>
+      <c r="E24" s="19">
         <v>2</v>
       </c>
-      <c r="F24" s="15"/>
-      <c r="I24" s="15">
+      <c r="F24" s="19"/>
+      <c r="I24" s="19">
         <v>7</v>
       </c>
-      <c r="J24" s="15"/>
-      <c r="M24" s="15">
+      <c r="J24" s="19"/>
+      <c r="M24" s="19">
         <v>10</v>
       </c>
-      <c r="N24" s="15"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N24" s="19"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>208</v>
       </c>
@@ -10407,7 +10571,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>209</v>
       </c>
@@ -10421,7 +10585,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>210</v>
       </c>
@@ -10432,7 +10596,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>211</v>
       </c>
@@ -10443,7 +10607,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>212</v>
       </c>
@@ -10454,7 +10618,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>213</v>
       </c>
@@ -10465,7 +10629,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
@@ -10495,7 +10659,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>28</v>
       </c>
@@ -10524,7 +10688,7 @@
         <v>5.7735026918962525E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -10542,7 +10706,7 @@
       <c r="O33" s="4"/>
       <c r="P33" s="4"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B34" s="10">
         <f>B21-B31</f>
         <v>2.2166666666666668</v>
@@ -10560,25 +10724,25 @@
         <v>12.666666666666668</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E37">
         <f>2.69-0.57</f>
         <v>2.12</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E38">
         <f>3.51-0.56</f>
         <v>2.9499999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E39">
         <f>9.81-0.52</f>
         <v>9.2900000000000009</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E40">
         <f>13.18-0.51</f>
         <v>12.67</v>
@@ -10586,53 +10750,53 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="M24:N24"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A13:O13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="M24:N24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P34"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>45980</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
@@ -10640,7 +10804,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>230</v>
       </c>
@@ -10651,7 +10815,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>231</v>
       </c>
@@ -10662,7 +10826,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>232</v>
       </c>
@@ -10673,7 +10837,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>174</v>
       </c>
@@ -10684,7 +10848,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>233</v>
       </c>
@@ -10695,7 +10859,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>171</v>
       </c>
@@ -10706,7 +10870,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -10731,43 +10895,43 @@
       <c r="M12" s="1"/>
       <c r="N12" s="2"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
       <c r="P13" s="4"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
         <v>0.02</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="E14" s="15">
+      <c r="B14" s="19"/>
+      <c r="E14" s="19">
         <v>0.05</v>
       </c>
-      <c r="F14" s="15"/>
-      <c r="I14" s="15">
+      <c r="F14" s="19"/>
+      <c r="I14" s="19">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>244</v>
       </c>
@@ -10778,7 +10942,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>245</v>
       </c>
@@ -10789,7 +10953,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>246</v>
       </c>
@@ -10800,7 +10964,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>247</v>
       </c>
@@ -10811,7 +10975,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>248</v>
       </c>
@@ -10822,7 +10986,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>249</v>
       </c>
@@ -10833,7 +10997,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
@@ -10858,7 +11022,7 @@
       <c r="M21" s="1"/>
       <c r="N21" s="2"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -10883,19 +11047,19 @@
       <c r="M22" s="1"/>
       <c r="N22" s="3"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -10903,23 +11067,23 @@
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="19">
         <v>0.02</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="E24" s="15">
+      <c r="B24" s="19"/>
+      <c r="E24" s="19">
         <v>0.05</v>
       </c>
-      <c r="F24" s="15"/>
-      <c r="I24" s="15">
+      <c r="F24" s="19"/>
+      <c r="I24" s="19">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>261</v>
       </c>
@@ -10930,7 +11094,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>262</v>
       </c>
@@ -10941,7 +11105,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>263</v>
       </c>
@@ -10952,7 +11116,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>264</v>
       </c>
@@ -10963,7 +11127,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>265</v>
       </c>
@@ -10974,7 +11138,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>264</v>
       </c>
@@ -10985,7 +11149,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
@@ -11010,7 +11174,7 @@
       <c r="M31" s="1"/>
       <c r="N31" s="2"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>28</v>
       </c>
@@ -11034,7 +11198,7 @@
       <c r="M32" s="1"/>
       <c r="N32" s="3"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -11052,7 +11216,7 @@
       <c r="O33" s="4"/>
       <c r="P33" s="4"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B34" s="10">
         <f>B21-B31</f>
         <v>9.6666666666666623E-2</v>
@@ -11072,53 +11236,53 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="M24:N24"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A13:O13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="M24:N24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P34"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>45994</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
@@ -11126,7 +11290,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E5" t="s">
         <v>275</v>
       </c>
@@ -11134,7 +11298,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E6" t="s">
         <v>241</v>
       </c>
@@ -11142,7 +11306,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E7" t="s">
         <v>276</v>
       </c>
@@ -11150,7 +11314,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E8" t="s">
         <v>241</v>
       </c>
@@ -11158,7 +11322,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E9" t="s">
         <v>277</v>
       </c>
@@ -11166,7 +11330,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E10" t="s">
         <v>104</v>
       </c>
@@ -11174,7 +11338,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="2"/>
       <c r="E12" s="1" t="s">
@@ -11192,45 +11356,45 @@
       <c r="M12" s="1"/>
       <c r="N12" s="2"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
       <c r="P13" s="4"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
         <v>0.02</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="E14" s="15">
+      <c r="B14" s="19"/>
+      <c r="E14" s="19">
         <v>0.05</v>
       </c>
-      <c r="F14" s="15"/>
-      <c r="I14" s="15">
+      <c r="F14" s="19"/>
+      <c r="I14" s="19">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J14" s="15"/>
-      <c r="M14" s="15">
+      <c r="J14" s="19"/>
+      <c r="M14" s="19">
         <v>0.09</v>
       </c>
-      <c r="N14" s="15"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N14" s="19"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>280</v>
       </c>
@@ -11244,7 +11408,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>281</v>
       </c>
@@ -11258,7 +11422,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>282</v>
       </c>
@@ -11272,7 +11436,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>283</v>
       </c>
@@ -11286,7 +11450,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>284</v>
       </c>
@@ -11300,7 +11464,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>285</v>
       </c>
@@ -11314,7 +11478,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
@@ -11342,7 +11506,7 @@
         <v>0.87666666666666659</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -11366,19 +11530,19 @@
       <c r="M22" s="1"/>
       <c r="N22" s="3"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -11386,25 +11550,25 @@
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="19">
         <v>0.02</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="E24" s="15">
+      <c r="B24" s="19"/>
+      <c r="E24" s="19">
         <v>0.05</v>
       </c>
-      <c r="F24" s="15"/>
-      <c r="I24" s="15">
+      <c r="F24" s="19"/>
+      <c r="I24" s="19">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J24" s="15"/>
-      <c r="M24" s="15">
+      <c r="J24" s="19"/>
+      <c r="M24" s="19">
         <v>0.09</v>
       </c>
-      <c r="N24" s="15"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N24" s="19"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>303</v>
       </c>
@@ -11418,7 +11582,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>304</v>
       </c>
@@ -11432,7 +11596,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>305</v>
       </c>
@@ -11446,7 +11610,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>306</v>
       </c>
@@ -11460,7 +11624,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>307</v>
       </c>
@@ -11474,7 +11638,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>308</v>
       </c>
@@ -11488,7 +11652,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
@@ -11518,7 +11682,7 @@
         <v>0.54666666666666675</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>28</v>
       </c>
@@ -11546,7 +11710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -11564,7 +11728,7 @@
       <c r="O33" s="4"/>
       <c r="P33" s="4"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B34" s="10">
         <f>B21-B31</f>
         <v>5.0000000000000044E-2</v>
@@ -11584,37 +11748,37 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="M24:N24"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A13:O13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="M24:N24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AE47"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45995</v>
       </c>
@@ -11635,38 +11799,38 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
-      <c r="U3" s="19" t="s">
+      <c r="U3" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="20"/>
-      <c r="Y3" s="20"/>
-      <c r="Z3" s="20"/>
-      <c r="AA3" s="20"/>
-      <c r="AB3" s="20"/>
-      <c r="AC3" s="20"/>
-      <c r="AD3" s="20"/>
-      <c r="AE3" s="20"/>
-    </row>
-    <row r="4" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="V3" s="22"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
+      <c r="Y3" s="22"/>
+      <c r="Z3" s="22"/>
+      <c r="AA3" s="22"/>
+      <c r="AB3" s="22"/>
+      <c r="AC3" s="22"/>
+      <c r="AD3" s="22"/>
+      <c r="AE3" s="22"/>
+    </row>
+    <row r="4" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
       <c r="Z4" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>323</v>
       </c>
@@ -11674,7 +11838,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>324</v>
       </c>
@@ -11682,7 +11846,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>297</v>
       </c>
@@ -11690,7 +11854,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>324</v>
       </c>
@@ -11698,17 +11862,17 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -11765,24 +11929,24 @@
         <v>1.4366666666666665</v>
       </c>
     </row>
-    <row r="13" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+    <row r="13" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
       <c r="T13" s="4" t="s">
         <v>101</v>
       </c>
@@ -11790,71 +11954,71 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
         <v>0.1</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="E14" s="15">
+      <c r="B14" s="19"/>
+      <c r="E14" s="19">
         <v>0.15</v>
       </c>
-      <c r="F14" s="15"/>
-      <c r="I14" s="15">
+      <c r="F14" s="19"/>
+      <c r="I14" s="19">
         <v>0.25</v>
       </c>
-      <c r="J14" s="15"/>
-      <c r="M14" s="15">
+      <c r="J14" s="19"/>
+      <c r="M14" s="19">
         <v>0.5</v>
       </c>
-      <c r="N14" s="15"/>
-      <c r="Q14" s="15">
+      <c r="N14" s="19"/>
+      <c r="Q14" s="19">
         <v>1</v>
       </c>
-      <c r="R14" s="15"/>
-      <c r="U14" s="15">
+      <c r="R14" s="19"/>
+      <c r="U14" s="19">
         <v>2.5</v>
       </c>
-      <c r="V14" s="15"/>
-      <c r="Y14" s="15">
+      <c r="V14" s="19"/>
+      <c r="Y14" s="19">
         <v>3</v>
       </c>
-      <c r="Z14" s="15"/>
-      <c r="AC14" s="15">
+      <c r="Z14" s="19"/>
+      <c r="AC14" s="19">
         <v>5</v>
       </c>
-      <c r="AD14" s="15"/>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AD14" s="19"/>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
@@ -11912,7 +12076,7 @@
         <v>6.4833333333333334</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -11970,88 +12134,88 @@
         <v>1.527525231651947E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
+    <row r="23" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
       <c r="T23" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A24" s="19">
         <v>0.1</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="E24" s="15">
+      <c r="B24" s="19"/>
+      <c r="E24" s="19">
         <v>0.15</v>
       </c>
-      <c r="F24" s="15"/>
-      <c r="I24" s="15">
+      <c r="F24" s="19"/>
+      <c r="I24" s="19">
         <v>0.25</v>
       </c>
-      <c r="J24" s="15"/>
-      <c r="M24" s="15">
+      <c r="J24" s="19"/>
+      <c r="M24" s="19">
         <v>0.5</v>
       </c>
-      <c r="N24" s="15"/>
-      <c r="Q24" s="15">
+      <c r="N24" s="19"/>
+      <c r="Q24" s="19">
         <v>1</v>
       </c>
-      <c r="R24" s="15"/>
-      <c r="U24" s="15">
+      <c r="R24" s="19"/>
+      <c r="U24" s="19">
         <v>2.5</v>
       </c>
-      <c r="V24" s="15"/>
-      <c r="Y24" s="15">
+      <c r="V24" s="19"/>
+      <c r="Y24" s="19">
         <v>3</v>
       </c>
-      <c r="Z24" s="15"/>
-      <c r="AC24" s="15">
+      <c r="Z24" s="19"/>
+      <c r="AC24" s="19">
         <v>5</v>
       </c>
-      <c r="AD24" s="15"/>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AD24" s="19"/>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
@@ -12109,7 +12273,7 @@
         <v>0.55333333333333334</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>28</v>
       </c>
@@ -12167,12 +12331,12 @@
         <v>1.5275252316519464E-3</v>
       </c>
     </row>
-    <row r="33" spans="2:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:30" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="T33" s="4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B34" s="10">
         <f>B21-B31</f>
         <v>0.30333333333333334</v>
@@ -12206,203 +12370,186 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C35" s="17" t="s">
+    <row r="35" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C35" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17" t="s">
+      <c r="D35" s="18"/>
+      <c r="E35" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17" t="s">
+      <c r="F35" s="18"/>
+      <c r="G35" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="14" t="s">
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="9" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="36" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C36" s="18">
+    <row r="36" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C36" s="14">
         <v>0.1</v>
       </c>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18" t="s">
+      <c r="D36" s="14"/>
+      <c r="E36" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18" t="s">
+      <c r="F36" s="14"/>
+      <c r="G36" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="13">
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="8">
         <v>0.42</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C37" s="18">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C37" s="14">
         <v>0.15</v>
       </c>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18" t="s">
+      <c r="D37" s="14"/>
+      <c r="E37" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18" t="s">
+      <c r="F37" s="14"/>
+      <c r="G37" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="13">
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C38" s="18">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C38" s="14">
         <v>0.25</v>
       </c>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18" t="s">
+      <c r="D38" s="14"/>
+      <c r="E38" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18" t="s">
+      <c r="F38" s="14"/>
+      <c r="G38" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="13">
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="8">
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C39" s="18">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C39" s="14">
         <v>0.5</v>
       </c>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18" t="s">
+      <c r="D39" s="14"/>
+      <c r="E39" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18" t="s">
+      <c r="F39" s="14"/>
+      <c r="G39" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="13">
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="8">
         <v>0.78</v>
       </c>
     </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C40" s="18">
+    <row r="40" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C40" s="14">
         <v>1</v>
       </c>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18" t="s">
+      <c r="D40" s="14"/>
+      <c r="E40" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18" t="s">
+      <c r="F40" s="14"/>
+      <c r="G40" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="13">
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="8">
         <v>1.43</v>
       </c>
     </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C41" s="18">
+    <row r="41" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C41" s="14">
         <v>2.5</v>
       </c>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18" t="s">
+      <c r="D41" s="14"/>
+      <c r="E41" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="F41" s="18"/>
-      <c r="G41" s="21" t="s">
+      <c r="F41" s="14"/>
+      <c r="G41" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="H41" s="22"/>
-      <c r="I41" s="23"/>
-      <c r="J41" s="13">
+      <c r="H41" s="16"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="8">
         <v>3.02</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C42" s="18">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C42" s="14">
         <v>3</v>
       </c>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18" t="s">
+      <c r="D42" s="14"/>
+      <c r="E42" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18" t="s">
+      <c r="F42" s="14"/>
+      <c r="G42" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="13">
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="8">
         <v>3.67</v>
       </c>
     </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C43" s="18">
+    <row r="43" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C43" s="14">
         <v>5</v>
       </c>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18" t="s">
+      <c r="D43" s="14"/>
+      <c r="E43" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18" t="s">
+      <c r="F43" s="14"/>
+      <c r="G43" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="13">
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="8">
         <v>5.93</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="G41:I41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="U3:AE3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="Y14:Z14"/>
     <mergeCell ref="AC14:AD14"/>
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A24:B24"/>
@@ -12413,16 +12560,33 @@
     <mergeCell ref="U24:V24"/>
     <mergeCell ref="Y24:Z24"/>
     <mergeCell ref="AC24:AD24"/>
-    <mergeCell ref="U3:AE3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="Y14:Z14"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="G42:I42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
